--- a/checklist_forms/025_divorce_mediation_checklist--checklist_forms.xlsx
+++ b/checklist_forms/025_divorce_mediation_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>joint_custody</t>
+          <t>financial_support</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Joint Custody</t>
+          <t>Financial Support</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>financial_support</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financial Support</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>client_expectations_choices</t>
+          <t>mediation_process_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>facilitative</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facilitative</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>facilitative</t>
+          <t>evaluative</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Facilitative</t>
+          <t>Evaluative</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>evaluative</t>
+          <t>evaluative_facilitative</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Evaluative</t>
+          <t>Evaluative Facilitative</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mediation_process_choices</t>
+          <t>mediation_goals2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>evaluative_facilitative</t>
+          <t>reach_agreement</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Evaluative Facilitative</t>
+          <t>Reach Agreement</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>reach_agreement</t>
+          <t>understand_needs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Reach Agreement</t>
+          <t>Understand Needs</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>understand_needs</t>
+          <t>clarify_expectations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Understand Needs</t>
+          <t>Clarify Expectations</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mediation_goals2_choices</t>
+          <t>communication_style2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>clarify_expectations</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Clarify Expectations</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>collaborative</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Collaborative</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>communication_style2_choices</t>
+          <t>conflict_level2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>collaborative</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Collaborative</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1726,29 +1726,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>conflict_level2_choices</t>
+          <t>priority_issues2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>emotional</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Emotional</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>emotional</t>
+          <t>practical</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Emotional</t>
+          <t>Practical</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>practical</t>
+          <t>spiritual</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Practical</t>
+          <t>Spiritual</t>
         </is>
       </c>
     </row>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>spiritual</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spiritual</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>priority_issues2_choices</t>
+          <t>client_emotions2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>financial</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Angry</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Sad</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>scared</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Scared</t>
         </is>
       </c>
     </row>
@@ -1862,29 +1862,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>scared</t>
+          <t>hopeful</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scared</t>
+          <t>Hopeful</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>client_emotions2_choices</t>
+          <t>client_expectations2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>hopeful</t>
+          <t>joint_custody</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hopeful</t>
+          <t>Joint Custody</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>joint_custody</t>
+          <t>custody_of_one_parent</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Joint Custody</t>
+          <t>Custody of One Parent</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>custody_of_one_parent</t>
+          <t>financial_support</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Custody of One Parent</t>
+          <t>Financial Support</t>
         </is>
       </c>
     </row>
@@ -1930,46 +1930,46 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>joint_custody</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Joint Custody</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>client_expectations2_choices</t>
+          <t>client_readiness2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>financial_support</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Financial Support</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>client_expectations2_choices</t>
+          <t>client_readiness2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1981,46 +1981,46 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>client_readiness2_choices</t>
+          <t>communication_style2_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>client_readiness2_choices</t>
+          <t>communication_style2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -2032,46 +2032,46 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>collaborative</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Collaborative</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>communication_style2_choices</t>
+          <t>conflict_level2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>communication_style2_choices</t>
+          <t>conflict_level2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>collaborative</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Collaborative</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2083,44 +2083,10 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>conflict_level2_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>conflict_level2_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
